--- a/Backtest/11-01-19/NASDAQstock_11-01-19period252RS90.xlsx
+++ b/Backtest/11-01-19/NASDAQstock_11-01-19period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="145">
   <si>
     <t>Stock</t>
   </si>
@@ -127,211 +127,328 @@
     <t>EM Rating</t>
   </si>
   <si>
-    <t>MPW</t>
-  </si>
-  <si>
-    <t>FOXF</t>
-  </si>
-  <si>
-    <t>DXCM</t>
-  </si>
-  <si>
-    <t>CTRE</t>
-  </si>
-  <si>
-    <t>TKO</t>
-  </si>
-  <si>
-    <t>VNDA</t>
+    <t>GLPG</t>
+  </si>
+  <si>
+    <t>EW</t>
+  </si>
+  <si>
+    <t>ETR</t>
+  </si>
+  <si>
+    <t>ARWR</t>
+  </si>
+  <si>
+    <t>BEP</t>
   </si>
   <si>
     <t>CROX</t>
   </si>
   <si>
-    <t>EXPO</t>
-  </si>
-  <si>
-    <t>IPAR</t>
-  </si>
-  <si>
-    <t>CQP</t>
-  </si>
-  <si>
-    <t>UI</t>
-  </si>
-  <si>
-    <t>EVTC</t>
-  </si>
-  <si>
-    <t>EVO</t>
-  </si>
-  <si>
-    <t>MOH</t>
-  </si>
-  <si>
-    <t>CCJ</t>
-  </si>
-  <si>
-    <t>AES</t>
-  </si>
-  <si>
-    <t>FE</t>
-  </si>
-  <si>
-    <t>MEDP</t>
-  </si>
-  <si>
-    <t>LADR</t>
-  </si>
-  <si>
-    <t>VEEV</t>
-  </si>
-  <si>
-    <t>GLOB</t>
-  </si>
-  <si>
-    <t>ORLY</t>
+    <t>ARES</t>
+  </si>
+  <si>
+    <t>APO</t>
+  </si>
+  <si>
+    <t>UPBD</t>
+  </si>
+  <si>
+    <t>SUI</t>
+  </si>
+  <si>
+    <t>CG</t>
+  </si>
+  <si>
+    <t>TPX</t>
+  </si>
+  <si>
+    <t>CRSP</t>
+  </si>
+  <si>
+    <t>DAVA</t>
+  </si>
+  <si>
+    <t>STX</t>
+  </si>
+  <si>
+    <t>KEYS</t>
+  </si>
+  <si>
+    <t>CCK</t>
+  </si>
+  <si>
+    <t>ACGL</t>
+  </si>
+  <si>
+    <t>KNSL</t>
+  </si>
+  <si>
+    <t>POOL</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>AMWD</t>
+  </si>
+  <si>
+    <t>AEM</t>
+  </si>
+  <si>
+    <t>NMIH</t>
+  </si>
+  <si>
+    <t>OMF</t>
+  </si>
+  <si>
+    <t>HUBB</t>
+  </si>
+  <si>
+    <t>VLRS</t>
+  </si>
+  <si>
+    <t>ANIP</t>
+  </si>
+  <si>
+    <t>XRAY</t>
+  </si>
+  <si>
+    <t>DIOD</t>
+  </si>
+  <si>
+    <t>EPRT</t>
+  </si>
+  <si>
+    <t>CPRT</t>
+  </si>
+  <si>
+    <t>SAH</t>
+  </si>
+  <si>
+    <t>ANSS</t>
+  </si>
+  <si>
+    <t>ELS</t>
+  </si>
+  <si>
+    <t>IBP</t>
+  </si>
+  <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>CSWI</t>
+  </si>
+  <si>
+    <t>TER</t>
+  </si>
+  <si>
+    <t>EQIX</t>
+  </si>
+  <si>
+    <t>CSGS</t>
+  </si>
+  <si>
+    <t>MV</t>
+  </si>
+  <si>
+    <t>M</t>
   </si>
   <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>2019-02-07</t>
-  </si>
-  <si>
-    <t>2019-02-26</t>
-  </si>
-  <si>
-    <t>2019-02-21</t>
-  </si>
-  <si>
-    <t>2019-02-13</t>
-  </si>
-  <si>
-    <t>2019-02-28</t>
-  </si>
-  <si>
-    <t>2019-01-31</t>
-  </si>
-  <si>
-    <t>2019-03-04</t>
-  </si>
-  <si>
-    <t>2019-02-08</t>
-  </si>
-  <si>
-    <t>2019-02-20</t>
-  </si>
-  <si>
-    <t>2019-03-19</t>
-  </si>
-  <si>
-    <t>2019-02-11</t>
-  </si>
-  <si>
-    <t>2019-02-27</t>
-  </si>
-  <si>
-    <t>2019-02-19</t>
-  </si>
-  <si>
-    <t>2019-02-25</t>
-  </si>
-  <si>
-    <t>2019-02-14</t>
-  </si>
-  <si>
-    <t>2019-02-06</t>
+    <t>2020-03-27</t>
+  </si>
+  <si>
+    <t>2020-01-30</t>
+  </si>
+  <si>
+    <t>2020-02-19</t>
+  </si>
+  <si>
+    <t>2019-11-25</t>
+  </si>
+  <si>
+    <t>2019-11-11</t>
+  </si>
+  <si>
+    <t>2020-02-27</t>
+  </si>
+  <si>
+    <t>2020-02-13</t>
+  </si>
+  <si>
+    <t>2019-11-06</t>
+  </si>
+  <si>
+    <t>2020-02-05</t>
+  </si>
+  <si>
+    <t>2020-02-12</t>
+  </si>
+  <si>
+    <t>2019-11-19</t>
+  </si>
+  <si>
+    <t>2020-02-04</t>
+  </si>
+  <si>
+    <t>2019-11-26</t>
+  </si>
+  <si>
+    <t>2020-02-11</t>
+  </si>
+  <si>
+    <t>2020-02-20</t>
+  </si>
+  <si>
+    <t>2020-02-10</t>
+  </si>
+  <si>
+    <t>2020-02-25</t>
+  </si>
+  <si>
+    <t>2019-11-07</t>
+  </si>
+  <si>
+    <t>2019-11-04</t>
+  </si>
+  <si>
+    <t>2019-11-20</t>
+  </si>
+  <si>
+    <t>2020-01-27</t>
+  </si>
+  <si>
+    <t>2019-11-05</t>
+  </si>
+  <si>
+    <t>2020-01-22</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Utilities</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Technology</t>
   </si>
   <si>
     <t>Real Estate</t>
   </si>
   <si>
-    <t>Consumer Cyclical</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Communication Services</t>
-  </si>
-  <si>
     <t>Industrials</t>
   </si>
   <si>
-    <t>Consumer Defensive</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Utilities</t>
-  </si>
-  <si>
-    <t>REIT - Healthcare Facilities</t>
-  </si>
-  <si>
-    <t>Auto Parts</t>
+    <t>Basic Materials</t>
+  </si>
+  <si>
+    <t>Biotechnology</t>
   </si>
   <si>
     <t>Medical Devices</t>
   </si>
   <si>
-    <t>Entertainment</t>
-  </si>
-  <si>
-    <t>Biotechnology</t>
+    <t>Utilities - Regulated Electric</t>
+  </si>
+  <si>
+    <t>Utilities - Renewable</t>
   </si>
   <si>
     <t>Footwear &amp; Accessories</t>
   </si>
   <si>
-    <t>Engineering &amp; Construction</t>
-  </si>
-  <si>
-    <t>Household &amp; Personal Products</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Midstream</t>
+    <t>Asset Management</t>
+  </si>
+  <si>
+    <t>Software - Application</t>
+  </si>
+  <si>
+    <t>REIT - Residential</t>
+  </si>
+  <si>
+    <t>Furnishings, Fixtures &amp; Appliances</t>
+  </si>
+  <si>
+    <t>Software - Infrastructure</t>
+  </si>
+  <si>
+    <t>Computer Hardware</t>
+  </si>
+  <si>
+    <t>Scientific &amp; Technical Instruments</t>
+  </si>
+  <si>
+    <t>Packaging &amp; Containers</t>
+  </si>
+  <si>
+    <t>Insurance - Diversified</t>
+  </si>
+  <si>
+    <t>Insurance - Property &amp; Casualty</t>
+  </si>
+  <si>
+    <t>Industrial Distribution</t>
+  </si>
+  <si>
+    <t>Building Products &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>Insurance - Specialty</t>
+  </si>
+  <si>
+    <t>Credit Services</t>
+  </si>
+  <si>
+    <t>Electrical Equipment &amp; Parts</t>
+  </si>
+  <si>
+    <t>Airlines</t>
+  </si>
+  <si>
+    <t>Drug Manufacturers - Specialty &amp; Generic</t>
+  </si>
+  <si>
+    <t>Medical Instruments &amp; Supplies</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>REIT - Diversified</t>
+  </si>
+  <si>
+    <t>Specialty Business Services</t>
+  </si>
+  <si>
+    <t>Auto &amp; Truck Dealerships</t>
+  </si>
+  <si>
+    <t>Residential Construction</t>
   </si>
   <si>
     <t>Communication Equipment</t>
   </si>
   <si>
-    <t>Software - Infrastructure</t>
-  </si>
-  <si>
-    <t>Drug Manufacturers - Specialty &amp; Generic</t>
-  </si>
-  <si>
-    <t>Healthcare Plans</t>
-  </si>
-  <si>
-    <t>Uranium</t>
-  </si>
-  <si>
-    <t>Utilities - Diversified</t>
-  </si>
-  <si>
-    <t>Utilities - Regulated Electric</t>
-  </si>
-  <si>
-    <t>Diagnostics &amp; Research</t>
-  </si>
-  <si>
-    <t>REIT - Mortgage</t>
-  </si>
-  <si>
-    <t>Health Information Services</t>
-  </si>
-  <si>
-    <t>Information Technology Services</t>
-  </si>
-  <si>
-    <t>Specialty Retail</t>
+    <t>Specialty Industrial Machinery</t>
+  </si>
+  <si>
+    <t>Semiconductor Equipment &amp; Materials</t>
+  </si>
+  <si>
+    <t>REIT - Specialty</t>
   </si>
 </sst>
 </file>
@@ -689,7 +806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK23"/>
+  <dimension ref="A1:AK42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -810,43 +927,43 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>91.92751235584844</v>
+        <v>96.8561872909699</v>
       </c>
       <c r="C2">
-        <v>232</v>
+        <v>1939</v>
       </c>
       <c r="D2">
-        <v>10.51</v>
+        <v>183.97</v>
       </c>
       <c r="E2">
         <v>2.46</v>
       </c>
       <c r="F2">
-        <v>-0.4263138510157587</v>
+        <v>0.7126221661999222</v>
       </c>
       <c r="G2">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="H2">
-        <v>-0.9669962297087964</v>
+        <v>0.1301375310956867</v>
       </c>
       <c r="I2">
-        <v>10.43214054107666</v>
+        <v>177.3899993896484</v>
       </c>
       <c r="J2">
-        <v>10.35103688240051</v>
+        <v>162.0404998779297</v>
       </c>
       <c r="K2">
-        <v>10.33684061050415</v>
+        <v>160.857399597168</v>
       </c>
       <c r="L2">
-        <v>9.029441895484924</v>
+        <v>133.4540495681763</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N2">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -873,46 +990,46 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>7.02</v>
+        <v>85</v>
       </c>
       <c r="Y2">
-        <v>10.98</v>
+        <v>191.63</v>
       </c>
       <c r="Z2">
-        <v>3.42</v>
+        <v>9.15</v>
       </c>
       <c r="AA2">
-        <v>74.36</v>
+        <v>-1.05</v>
       </c>
       <c r="AB2">
-        <v>198.91</v>
+        <v>648.05</v>
       </c>
       <c r="AC2">
-        <v>957.89</v>
+        <v>1642.02</v>
       </c>
       <c r="AD2">
-        <v>16.42</v>
+        <v>14.25</v>
       </c>
       <c r="AE2">
-        <v>570</v>
+        <v>820.16</v>
       </c>
       <c r="AF2">
-        <v>20</v>
+        <v>4.35</v>
       </c>
       <c r="AG2">
-        <v>31.58</v>
+        <v>-352.9</v>
       </c>
       <c r="AH2" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="AI2" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AJ2" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="AK2">
-        <v>73.0840694598036</v>
+        <v>72.53958838484766</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -920,43 +1037,43 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>96.65803718522005</v>
+        <v>94.98327759197325</v>
       </c>
       <c r="C3">
-        <v>1942</v>
+        <v>281</v>
       </c>
       <c r="D3">
-        <v>64.87</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="E3">
-        <v>3.13</v>
+        <v>1.74</v>
       </c>
       <c r="F3">
-        <v>0.3845075894967933</v>
+        <v>-0.0958561714719343</v>
       </c>
       <c r="G3">
-        <v>3.88</v>
+        <v>1.64</v>
       </c>
       <c r="H3">
-        <v>0.9608925564825014</v>
+        <v>-0.4175086774741398</v>
       </c>
       <c r="I3">
-        <v>62.31200103759765</v>
+        <v>78.76466674804688</v>
       </c>
       <c r="J3">
-        <v>59.5305004119873</v>
+        <v>76.20449981689453</v>
       </c>
       <c r="K3">
-        <v>62.79320014953613</v>
+        <v>74.22033340454101</v>
       </c>
       <c r="L3">
-        <v>53.913450050354</v>
+        <v>64.8513166809082</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N3">
-        <v>0.99</v>
+        <v>1.06</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -983,46 +1100,46 @@
         <v>1</v>
       </c>
       <c r="X3">
-        <v>33.2</v>
+        <v>46.55</v>
       </c>
       <c r="Y3">
-        <v>76.77</v>
+        <v>80.52</v>
       </c>
       <c r="Z3">
-        <v>2.74</v>
+        <v>46.64</v>
       </c>
       <c r="AA3">
-        <v>62.58</v>
+        <v>12.93</v>
       </c>
       <c r="AB3">
-        <v>23.94</v>
+        <v>8.42</v>
       </c>
       <c r="AC3">
-        <v>814.29</v>
+        <v>3208.27</v>
       </c>
       <c r="AD3">
-        <v>8.279999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AE3">
-        <v>30.61</v>
+        <v>12.82</v>
       </c>
       <c r="AF3">
-        <v>-12.5</v>
+        <v>-2.5</v>
       </c>
       <c r="AG3">
-        <v>700</v>
+        <v>2907.52</v>
       </c>
       <c r="AH3" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="AI3" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="AJ3" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="AK3">
-        <v>66.21177349175196</v>
+        <v>68.56379205632767</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1030,49 +1147,49 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>98.87032242880677</v>
+        <v>93.22185061315497</v>
       </c>
       <c r="C4">
-        <v>125</v>
+        <v>261</v>
       </c>
       <c r="D4">
-        <v>35.47</v>
+        <v>45.95</v>
       </c>
       <c r="E4">
-        <v>4.08</v>
+        <v>0.97</v>
       </c>
       <c r="F4">
-        <v>1.534179781268323</v>
+        <v>-0.960478838148781</v>
       </c>
       <c r="G4">
-        <v>3.85</v>
+        <v>0.82</v>
       </c>
       <c r="H4">
-        <v>0.9321180969871091</v>
+        <v>-1.70056550898059</v>
       </c>
       <c r="I4">
-        <v>32.91799964904785</v>
+        <v>45.42546997070313</v>
       </c>
       <c r="J4">
-        <v>29.93287496566773</v>
+        <v>44.85450057983398</v>
       </c>
       <c r="K4">
-        <v>31.66394992828369</v>
+        <v>43.90588890075684</v>
       </c>
       <c r="L4">
-        <v>27.92037497520447</v>
+        <v>37.9165415763855</v>
       </c>
       <c r="M4">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1081,10 +1198,10 @@
         <v>0</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.888888888888888</v>
       </c>
       <c r="U4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="b">
         <v>1</v>
@@ -1093,46 +1210,46 @@
         <v>0</v>
       </c>
       <c r="X4">
-        <v>13.23</v>
+        <v>28.65</v>
       </c>
       <c r="Y4">
-        <v>38.03</v>
+        <v>46.05</v>
       </c>
       <c r="Z4">
-        <v>12.92</v>
+        <v>8.9</v>
       </c>
       <c r="AA4">
-        <v>-134.43</v>
+        <v>2.2</v>
       </c>
       <c r="AB4">
-        <v>173.13</v>
+        <v>100.5</v>
       </c>
       <c r="AC4">
-        <v>630</v>
+        <v>597.3</v>
       </c>
       <c r="AD4">
-        <v>8.289999999999999</v>
+        <v>3.68</v>
       </c>
       <c r="AE4">
-        <v>55.88</v>
+        <v>50.82</v>
       </c>
       <c r="AF4">
-        <v>221.43</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="AG4">
-        <v>-180</v>
+        <v>462.16</v>
       </c>
       <c r="AH4" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="AI4" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="AJ4" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="AK4">
-        <v>65.03454828957076</v>
+        <v>65.00909451988301</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1140,43 +1257,46 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>90.51541539185692</v>
+        <v>99.62095875139353</v>
       </c>
       <c r="C5">
-        <v>724</v>
+        <v>851</v>
       </c>
       <c r="D5">
-        <v>14.77</v>
+        <v>40.05</v>
       </c>
       <c r="E5">
-        <v>2.24</v>
+        <v>3.02</v>
       </c>
       <c r="F5">
-        <v>-0.6925537270049545</v>
+        <v>1.341438651055811</v>
       </c>
       <c r="G5">
-        <v>1.85</v>
+        <v>3.47</v>
       </c>
       <c r="H5">
-        <v>-0.9861792027057247</v>
+        <v>2.445898641619524</v>
       </c>
       <c r="I5">
-        <v>14.20213088989258</v>
+        <v>39.55799942016601</v>
       </c>
       <c r="J5">
-        <v>14.15959591865539</v>
+        <v>35.69299964904785</v>
       </c>
       <c r="K5">
-        <v>14.19635208129883</v>
+        <v>32.50859985351563</v>
       </c>
       <c r="L5">
-        <v>12.46227156639099</v>
+        <v>24.64352499961853</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>1.22</v>
+      </c>
+      <c r="O5" t="s">
+        <v>14</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1185,13 +1305,13 @@
         <v>0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>7.222222222222221</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
@@ -1200,49 +1320,49 @@
         <v>1</v>
       </c>
       <c r="W5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5">
-        <v>9.08</v>
+        <v>10.41</v>
       </c>
       <c r="Y5">
-        <v>15.27</v>
+        <v>40.65</v>
       </c>
       <c r="Z5">
-        <v>1.07</v>
+        <v>2.62</v>
       </c>
       <c r="AA5">
-        <v>112000</v>
+        <v>-3.85</v>
       </c>
       <c r="AB5">
-        <v>12</v>
+        <v>160</v>
       </c>
       <c r="AC5">
-        <v>800</v>
+        <v>290.91</v>
       </c>
       <c r="AD5">
-        <v>2.02</v>
+        <v>9.01</v>
       </c>
       <c r="AE5">
-        <v>5.88</v>
+        <v>-16</v>
       </c>
       <c r="AF5">
-        <v>-10.53</v>
+        <v>92.31</v>
       </c>
       <c r="AG5">
-        <v>850</v>
+        <v>218.18</v>
       </c>
       <c r="AH5" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="AI5" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AJ5" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="AK5">
-        <v>64.67707395442204</v>
+        <v>64.99806919078472</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1250,49 +1370,49 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>98.82325253000705</v>
+        <v>93.91304347826087</v>
       </c>
       <c r="C6">
-        <v>921</v>
+        <v>1691</v>
       </c>
       <c r="D6">
-        <v>73.18000000000001</v>
+        <v>18.37</v>
       </c>
       <c r="E6">
-        <v>3.35</v>
+        <v>1.13</v>
       </c>
       <c r="F6">
-        <v>0.6507474654859897</v>
+        <v>-0.780816985332813</v>
       </c>
       <c r="G6">
-        <v>3.48</v>
+        <v>0.97</v>
       </c>
       <c r="H6">
-        <v>0.5772330965439347</v>
+        <v>-1.465859991022093</v>
       </c>
       <c r="I6">
-        <v>73.39247283935546</v>
+        <v>18.14190483093262</v>
       </c>
       <c r="J6">
-        <v>68.95466861724853</v>
+        <v>18.10498237609863</v>
       </c>
       <c r="K6">
-        <v>66.34613456726075</v>
+        <v>17.06209087371826</v>
       </c>
       <c r="L6">
-        <v>64.03097385406494</v>
+        <v>14.61283386707306</v>
       </c>
       <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
         <v>1.06</v>
       </c>
-      <c r="N6">
-        <v>1.11</v>
-      </c>
       <c r="P6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -1301,58 +1421,58 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="U6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" t="b">
         <v>1</v>
       </c>
       <c r="W6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6">
-        <v>28.71</v>
+        <v>10.26</v>
       </c>
       <c r="Y6">
-        <v>90.54000000000001</v>
+        <v>18.55</v>
       </c>
       <c r="Z6">
-        <v>8.140000000000001</v>
+        <v>3.98</v>
       </c>
       <c r="AA6">
-        <v>10250</v>
+        <v>48.67</v>
       </c>
       <c r="AB6">
-        <v>54.72</v>
+        <v>157.66</v>
       </c>
       <c r="AC6">
-        <v>514.29</v>
+        <v>127.75</v>
       </c>
       <c r="AD6">
-        <v>12.03</v>
+        <v>0.66</v>
       </c>
       <c r="AE6">
-        <v>230.77</v>
+        <v>-64.31</v>
       </c>
       <c r="AF6">
-        <v>-31.58</v>
+        <v>-51.73</v>
       </c>
       <c r="AG6">
-        <v>171.43</v>
+        <v>261.08</v>
       </c>
       <c r="AH6" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AI6" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AJ6" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="AK6">
-        <v>59.15346691012671</v>
+        <v>63.80890927299825</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1360,58 +1480,61 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>98.16427394681101</v>
+        <v>94.71571906354515</v>
       </c>
       <c r="C7">
-        <v>1199</v>
+        <v>199</v>
       </c>
       <c r="D7">
-        <v>28.89</v>
+        <v>34.99</v>
       </c>
       <c r="E7">
-        <v>3.26</v>
+        <v>4.38</v>
       </c>
       <c r="F7">
-        <v>0.5418311525813182</v>
+        <v>2.86856439999154</v>
       </c>
       <c r="G7">
-        <v>5.02</v>
+        <v>3.19</v>
       </c>
       <c r="H7">
-        <v>2.054322017307416</v>
+        <v>2.007781674763663</v>
       </c>
       <c r="I7">
-        <v>28.55</v>
+        <v>34.97400054931641</v>
       </c>
       <c r="J7">
-        <v>26.28850002288818</v>
+        <v>32.35350017547607</v>
       </c>
       <c r="K7">
-        <v>24.76859992980957</v>
+        <v>28.66619998931885</v>
       </c>
       <c r="L7">
-        <v>20.41800002098083</v>
+        <v>25.4353000164032</v>
       </c>
       <c r="M7">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
-        <v>1.15</v>
+        <v>1.22</v>
+      </c>
+      <c r="O7" t="s">
+        <v>78</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R7">
         <v>0</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
@@ -1423,46 +1546,46 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>13.88</v>
+        <v>17.52</v>
       </c>
       <c r="Y7">
-        <v>33.44</v>
+        <v>39.13</v>
       </c>
       <c r="Z7">
-        <v>1.26</v>
+        <v>1.95</v>
       </c>
       <c r="AA7">
-        <v>-6.04</v>
+        <v>4.16</v>
       </c>
       <c r="AB7">
-        <v>171.43</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="AC7">
-        <v>380</v>
+        <v>132.3</v>
       </c>
       <c r="AD7">
-        <v>2.74</v>
+        <v>30.36</v>
       </c>
       <c r="AE7">
-        <v>55.56</v>
+        <v>-5.45</v>
       </c>
       <c r="AF7">
-        <v>28.57</v>
+        <v>61.76</v>
       </c>
       <c r="AG7">
-        <v>240</v>
+        <v>121.12</v>
       </c>
       <c r="AH7" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="AI7" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="AJ7" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="AK7">
-        <v>55.61986732281166</v>
+        <v>63.59440343142424</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1470,46 +1593,46 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>98.49376323840903</v>
+        <v>94.00222965440356</v>
       </c>
       <c r="C8">
-        <v>653</v>
+        <v>1182</v>
       </c>
       <c r="D8">
-        <v>31.1</v>
+        <v>24.88</v>
       </c>
       <c r="E8">
-        <v>3.42</v>
+        <v>1.7</v>
       </c>
       <c r="F8">
-        <v>0.7354601533007338</v>
+        <v>-0.1407716346759264</v>
       </c>
       <c r="G8">
-        <v>4.86</v>
+        <v>2.21</v>
       </c>
       <c r="H8">
-        <v>1.90085823333199</v>
+        <v>0.474372290768149</v>
       </c>
       <c r="I8">
-        <v>29.89400024414062</v>
+        <v>24.66004791259765</v>
       </c>
       <c r="J8">
-        <v>26.73199996948242</v>
+        <v>23.20420980453491</v>
       </c>
       <c r="K8">
-        <v>25.71540000915527</v>
+        <v>23.81554824829102</v>
       </c>
       <c r="L8">
-        <v>20.12464998245239</v>
+        <v>21.4667036151886</v>
       </c>
       <c r="M8">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="N8">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1518,10 +1641,10 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>1.666666666666667</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
@@ -1533,46 +1656,46 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>12.02</v>
+        <v>13.13</v>
       </c>
       <c r="Y8">
-        <v>31.88</v>
+        <v>26.11</v>
       </c>
       <c r="Z8">
-        <v>1.55</v>
+        <v>2.75</v>
       </c>
       <c r="AA8">
-        <v>843.75</v>
+        <v>93.02</v>
       </c>
       <c r="AB8">
-        <v>142.86</v>
+        <v>22.86</v>
       </c>
       <c r="AC8">
-        <v>124.24</v>
+        <v>1100</v>
       </c>
       <c r="AD8">
-        <v>5.32</v>
+        <v>5.95</v>
       </c>
       <c r="AE8">
-        <v>-78.38</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>146.67</v>
+        <v>-33.33</v>
       </c>
       <c r="AG8">
-        <v>145.45</v>
+        <v>1700</v>
       </c>
       <c r="AH8" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="AI8" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AJ8" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="AK8">
-        <v>54.56294567780806</v>
+        <v>62.52567285092177</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1580,46 +1703,46 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>93.95151800423629</v>
+        <v>90.5685618729097</v>
       </c>
       <c r="C9">
-        <v>1943</v>
+        <v>554</v>
       </c>
       <c r="D9">
-        <v>48.44</v>
+        <v>35.12</v>
       </c>
       <c r="E9">
-        <v>2.18</v>
+        <v>1.13</v>
       </c>
       <c r="F9">
-        <v>-0.7651646022747354</v>
+        <v>-0.780816985332813</v>
       </c>
       <c r="G9">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="H9">
-        <v>-0.9094473107180114</v>
+        <v>0.3179019454624842</v>
       </c>
       <c r="I9">
-        <v>48.18345642089844</v>
+        <v>35.12521591186523</v>
       </c>
       <c r="J9">
-        <v>46.7909408569336</v>
+        <v>33.93071231842041</v>
       </c>
       <c r="K9">
-        <v>47.40465698242188</v>
+        <v>33.48738201141357</v>
       </c>
       <c r="L9">
-        <v>45.86586725234985</v>
+        <v>28.00864567756653</v>
       </c>
       <c r="M9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N9">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1628,13 +1751,13 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>5.555555555555556</v>
       </c>
       <c r="U9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" t="b">
         <v>1</v>
@@ -1643,46 +1766,46 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>32.47</v>
+        <v>18.39</v>
       </c>
       <c r="Y9">
-        <v>51.2</v>
+        <v>35.89</v>
       </c>
       <c r="Z9">
-        <v>2.73</v>
+        <v>6.7</v>
       </c>
       <c r="AA9">
-        <v>26.75</v>
+        <v>15.66</v>
       </c>
       <c r="AB9">
-        <v>1.53</v>
+        <v>230.16</v>
       </c>
       <c r="AC9">
-        <v>540</v>
+        <v>267.35</v>
       </c>
       <c r="AD9">
-        <v>5.28</v>
+        <v>22.77</v>
       </c>
       <c r="AE9">
-        <v>-5.71</v>
+        <v>118.67</v>
       </c>
       <c r="AF9">
-        <v>-10.26</v>
+        <v>11.94</v>
       </c>
       <c r="AG9">
-        <v>620</v>
+        <v>168.37</v>
       </c>
       <c r="AH9" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="AI9" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="AJ9" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="AK9">
-        <v>54.33973900916884</v>
+        <v>62.22331589904812</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1690,43 +1813,43 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>93.26900447164039</v>
+        <v>96.92307692307692</v>
       </c>
       <c r="C10">
-        <v>2192</v>
+        <v>1315</v>
       </c>
       <c r="D10">
-        <v>55.03</v>
+        <v>20.49</v>
       </c>
       <c r="E10">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="F10">
-        <v>-0.934589977904224</v>
+        <v>0.55541804498595</v>
       </c>
       <c r="G10">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="H10">
-        <v>-0.880672851222619</v>
+        <v>0.4274311871764499</v>
       </c>
       <c r="I10">
-        <v>56.0745132446289</v>
+        <v>20.68553085327148</v>
       </c>
       <c r="J10">
-        <v>56.4546558380127</v>
+        <v>20.76791324615478</v>
       </c>
       <c r="K10">
-        <v>54.79277114868164</v>
+        <v>20.44654010772705</v>
       </c>
       <c r="L10">
-        <v>51.40378410339355</v>
+        <v>18.5462450170517</v>
       </c>
       <c r="M10">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="N10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -1750,49 +1873,49 @@
         <v>0</v>
       </c>
       <c r="W10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>36.63</v>
+        <v>9.4</v>
       </c>
       <c r="Y10">
-        <v>60.37</v>
+        <v>22.16</v>
       </c>
       <c r="Z10">
-        <v>1.83</v>
+        <v>1.16</v>
       </c>
       <c r="AA10">
-        <v>1.56</v>
+        <v>9.48</v>
       </c>
       <c r="AB10">
-        <v>9.66</v>
+        <v>290.91</v>
       </c>
       <c r="AC10">
-        <v>361.54</v>
+        <v>625</v>
       </c>
       <c r="AD10">
-        <v>4.15</v>
+        <v>24.1</v>
       </c>
       <c r="AE10">
-        <v>71.43000000000001</v>
+        <v>1142.86</v>
       </c>
       <c r="AF10">
-        <v>-31.37</v>
+        <v>366.67</v>
       </c>
       <c r="AG10">
-        <v>292.31</v>
+        <v>-87.5</v>
       </c>
       <c r="AH10" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="AI10" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="AJ10" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="AK10">
-        <v>49.54525274542026</v>
+        <v>61.36334407752403</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1800,49 +1923,49 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>92.37467639444576</v>
+        <v>94.55964325529543</v>
       </c>
       <c r="C11">
-        <v>1982</v>
+        <v>1347</v>
       </c>
       <c r="D11">
-        <v>25.36</v>
+        <v>144.16</v>
       </c>
       <c r="E11">
-        <v>2.12</v>
+        <v>0.77</v>
       </c>
       <c r="F11">
-        <v>-0.8377754775445163</v>
+        <v>-1.185056154168741</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="H11">
-        <v>-0.8423069052287623</v>
+        <v>-1.356330749308128</v>
       </c>
       <c r="I11">
-        <v>25.13248100280762</v>
+        <v>141.4306488037109</v>
       </c>
       <c r="J11">
-        <v>24.52215366363525</v>
+        <v>137.6483520507813</v>
       </c>
       <c r="K11">
-        <v>23.89023010253906</v>
+        <v>133.4694493103027</v>
       </c>
       <c r="L11">
-        <v>23.05936096191406</v>
+        <v>114.586791343689</v>
       </c>
       <c r="M11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N11">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -1851,58 +1974,58 @@
         <v>0</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="U11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" t="b">
         <v>1</v>
       </c>
       <c r="W11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>17.48</v>
+        <v>83.86</v>
       </c>
       <c r="Y11">
-        <v>26.36</v>
+        <v>144.67</v>
       </c>
       <c r="Z11">
-        <v>12.41</v>
+        <v>11.89</v>
       </c>
       <c r="AA11">
-        <v>-8197.530000000001</v>
+        <v>113.21</v>
       </c>
       <c r="AB11">
-        <v>8400</v>
+        <v>15.22</v>
       </c>
       <c r="AC11">
-        <v>158.88</v>
+        <v>530</v>
       </c>
       <c r="AD11">
-        <v>41.04</v>
+        <v>1.8</v>
       </c>
       <c r="AE11">
-        <v>8.619999999999999</v>
+        <v>36.96</v>
       </c>
       <c r="AF11">
-        <v>-15.94</v>
+        <v>15</v>
       </c>
       <c r="AG11">
-        <v>164.49</v>
+        <v>300</v>
       </c>
       <c r="AH11" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="AI11" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AJ11" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="AK11">
-        <v>46.63570844553284</v>
+        <v>57.47079438414563</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1910,46 +2033,46 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>93.85737820663685</v>
+        <v>91.59420289855072</v>
       </c>
       <c r="C12">
-        <v>1757</v>
+        <v>926</v>
       </c>
       <c r="D12">
-        <v>100.65</v>
+        <v>22.97</v>
       </c>
       <c r="E12">
-        <v>2.67</v>
+        <v>1.08</v>
       </c>
       <c r="F12">
-        <v>-0.172175787571526</v>
+        <v>-0.8369613143378027</v>
       </c>
       <c r="G12">
-        <v>3.37</v>
+        <v>1.9</v>
       </c>
       <c r="H12">
-        <v>0.471726745060829</v>
+        <v>-0.0106857796794116</v>
       </c>
       <c r="I12">
-        <v>97.76016998291016</v>
+        <v>23.093896484375</v>
       </c>
       <c r="J12">
-        <v>95.76293601989747</v>
+        <v>22.3411093711853</v>
       </c>
       <c r="K12">
-        <v>97.0973927307129</v>
+        <v>21.40526195526123</v>
       </c>
       <c r="L12">
-        <v>83.37453927993775</v>
+        <v>18.01581217765808</v>
       </c>
       <c r="M12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N12">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -1961,58 +2084,58 @@
         <v>0</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="U12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="b">
         <v>0</v>
       </c>
       <c r="X12">
-        <v>46.38</v>
+        <v>12.08</v>
       </c>
       <c r="Y12">
-        <v>108.93</v>
+        <v>23.54</v>
       </c>
       <c r="Z12">
-        <v>6.88</v>
+        <v>2.69</v>
       </c>
       <c r="AA12">
-        <v>18.95</v>
+        <v>7.46</v>
       </c>
       <c r="AB12">
-        <v>8.630000000000001</v>
+        <v>118.12</v>
       </c>
       <c r="AC12">
-        <v>275.76</v>
+        <v>433.33</v>
       </c>
       <c r="AD12">
-        <v>31.67</v>
+        <v>7.65</v>
       </c>
       <c r="AE12">
-        <v>24.73</v>
+        <v>-55.22</v>
       </c>
       <c r="AF12">
-        <v>-30.6</v>
+        <v>7.2</v>
       </c>
       <c r="AG12">
-        <v>303.03</v>
+        <v>794.4400000000001</v>
       </c>
       <c r="AH12" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="AI12" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="AJ12" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="AK12">
-        <v>44.32875347991863</v>
+        <v>56.62729259954571</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2020,49 +2143,49 @@
         <v>48</v>
       </c>
       <c r="B13">
-        <v>98.14073899741116</v>
+        <v>97.61426978818282</v>
       </c>
       <c r="C13">
-        <v>1185</v>
+        <v>170</v>
       </c>
       <c r="D13">
-        <v>27.45</v>
+        <v>21.84</v>
       </c>
       <c r="E13">
-        <v>2.17</v>
+        <v>2.87</v>
       </c>
       <c r="F13">
-        <v>-0.7772664148196992</v>
+        <v>1.173005664040841</v>
       </c>
       <c r="G13">
-        <v>3.33</v>
+        <v>2.56</v>
       </c>
       <c r="H13">
-        <v>0.4333607990669723</v>
+        <v>1.022018499337976</v>
       </c>
       <c r="I13">
-        <v>27.71503105163574</v>
+        <v>20.03747100830078</v>
       </c>
       <c r="J13">
-        <v>26.99784717559815</v>
+        <v>19.20329732894897</v>
       </c>
       <c r="K13">
-        <v>26.50154365539551</v>
+        <v>18.64256187438965</v>
       </c>
       <c r="L13">
-        <v>22.63648468971252</v>
+        <v>16.3160719537735</v>
       </c>
       <c r="M13">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N13">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -2071,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="U13" t="b">
         <v>0</v>
@@ -2083,46 +2206,46 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>13</v>
+        <v>9.34</v>
       </c>
       <c r="Y13">
-        <v>29.19</v>
+        <v>22</v>
       </c>
       <c r="Z13">
-        <v>1.74</v>
+        <v>4.14</v>
       </c>
       <c r="AA13">
-        <v>44.55</v>
+        <v>44.72</v>
       </c>
       <c r="AB13">
-        <v>3.09</v>
+        <v>3.66</v>
       </c>
       <c r="AC13">
-        <v>300</v>
+        <v>538.1</v>
       </c>
       <c r="AD13">
-        <v>10.74</v>
+        <v>21.52</v>
       </c>
       <c r="AE13">
-        <v>14.29</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="AF13">
-        <v>-12.5</v>
+        <v>46.15</v>
       </c>
       <c r="AG13">
-        <v>300</v>
+        <v>147.62</v>
       </c>
       <c r="AH13" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="AI13" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AJ13" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AK13">
-        <v>44.3082474297388</v>
+        <v>53.60684072015486</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2130,43 +2253,43 @@
         <v>49</v>
       </c>
       <c r="B14">
-        <v>92.13932690044716</v>
+        <v>93.40022296544036</v>
       </c>
       <c r="C14">
-        <v>3729</v>
+        <v>856</v>
       </c>
       <c r="D14">
-        <v>11.48</v>
+        <v>50.37</v>
       </c>
       <c r="E14">
-        <v>2.61</v>
+        <v>4.63</v>
       </c>
       <c r="F14">
-        <v>-0.2447866628413068</v>
+        <v>3.14928604501649</v>
       </c>
       <c r="G14">
-        <v>2.88</v>
+        <v>3.51</v>
       </c>
       <c r="H14">
-        <v>0.001743906636084512</v>
+        <v>2.50848677974179</v>
       </c>
       <c r="I14">
-        <v>10.94700012207031</v>
+        <v>47.20599899291992</v>
       </c>
       <c r="J14">
-        <v>10.18487505912781</v>
+        <v>40.54349975585937</v>
       </c>
       <c r="K14">
-        <v>10.4827499961853</v>
+        <v>43.59980003356934</v>
       </c>
       <c r="L14">
-        <v>9.94556248664856</v>
+        <v>41.22335004806519</v>
       </c>
       <c r="M14">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="N14">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2190,49 +2313,49 @@
         <v>1</v>
       </c>
       <c r="W14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>7.37</v>
+        <v>22.22</v>
       </c>
       <c r="Y14">
-        <v>13.12</v>
+        <v>53.9</v>
       </c>
       <c r="Z14">
-        <v>3.15</v>
+        <v>2.36</v>
       </c>
       <c r="AA14">
-        <v>-173.01</v>
+        <v>0.02</v>
       </c>
       <c r="AB14">
-        <v>59.85</v>
+        <v>89.8</v>
       </c>
       <c r="AC14">
-        <v>187.1</v>
+        <v>370.97</v>
       </c>
       <c r="AD14">
-        <v>8.82</v>
+        <v>23.39</v>
       </c>
       <c r="AE14">
-        <v>122.5</v>
+        <v>349.5</v>
       </c>
       <c r="AF14">
-        <v>500</v>
+        <v>-8.6</v>
       </c>
       <c r="AG14">
-        <v>-78.48999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="AI14" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="AJ14" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK14">
-        <v>40.54675407883377</v>
+        <v>53.52904301193375</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2240,43 +2363,43 @@
         <v>50</v>
       </c>
       <c r="B15">
-        <v>95.24594022122852</v>
+        <v>97.32441471571906</v>
       </c>
       <c r="C15">
-        <v>720</v>
+        <v>2380</v>
       </c>
       <c r="D15">
-        <v>133.04</v>
+        <v>43.01</v>
       </c>
       <c r="E15">
-        <v>4.77</v>
+        <v>2.07</v>
       </c>
       <c r="F15">
-        <v>2.369204846870801</v>
+        <v>0.2746963999609998</v>
       </c>
       <c r="G15">
-        <v>3.66</v>
+        <v>2.42</v>
       </c>
       <c r="H15">
-        <v>0.7498798535162899</v>
+        <v>0.8029600159100448</v>
       </c>
       <c r="I15">
-        <v>123.8699981689453</v>
+        <v>42.50799942016602</v>
       </c>
       <c r="J15">
-        <v>120.0979995727539</v>
+        <v>39.92849998474121</v>
       </c>
       <c r="K15">
-        <v>126.1186001586914</v>
+        <v>38.83400001525879</v>
       </c>
       <c r="L15">
-        <v>114.762149848938</v>
+        <v>33.83285004615784</v>
       </c>
       <c r="M15">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N15">
-        <v>0.98</v>
+        <v>1.09</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2300,49 +2423,49 @@
         <v>1</v>
       </c>
       <c r="W15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15">
-        <v>71.06999999999999</v>
+        <v>21.42</v>
       </c>
       <c r="Y15">
-        <v>154.06</v>
+        <v>44.99</v>
       </c>
       <c r="Z15">
-        <v>10.1</v>
+        <v>2.21</v>
       </c>
       <c r="AA15">
-        <v>24.96</v>
+        <v>0.28</v>
       </c>
       <c r="AB15">
-        <v>136.76</v>
+        <v>207.37</v>
       </c>
       <c r="AC15">
-        <v>169.25</v>
+        <v>296.93</v>
       </c>
       <c r="AD15">
-        <v>12.62</v>
+        <v>4.94</v>
       </c>
       <c r="AE15">
-        <v>-2.13</v>
+        <v>22.15</v>
       </c>
       <c r="AF15">
-        <v>83.8</v>
+        <v>-12.28</v>
       </c>
       <c r="AG15">
-        <v>138.49</v>
+        <v>270.44</v>
       </c>
       <c r="AH15" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="AI15" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AJ15" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="AK15">
-        <v>40.20139304463874</v>
+        <v>53.44410788058265</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2350,58 +2473,61 @@
         <v>51</v>
       </c>
       <c r="B16">
-        <v>90.77429983525536</v>
+        <v>93.57859531772576</v>
       </c>
       <c r="C16">
-        <v>584</v>
+        <v>414</v>
       </c>
       <c r="D16">
-        <v>12</v>
+        <v>47.16</v>
       </c>
       <c r="E16">
-        <v>2.23</v>
+        <v>1.37</v>
       </c>
       <c r="F16">
-        <v>-0.7046555395499183</v>
+        <v>-0.5113242061088604</v>
       </c>
       <c r="G16">
-        <v>2.45</v>
+        <v>1.78</v>
       </c>
       <c r="H16">
-        <v>-0.4106900127978745</v>
+        <v>-0.1984501940462091</v>
       </c>
       <c r="I16">
-        <v>11.68620281219482</v>
+        <v>46.8939712524414</v>
       </c>
       <c r="J16">
-        <v>11.22534327507019</v>
+        <v>44.83752536773682</v>
       </c>
       <c r="K16">
-        <v>11.33087184906006</v>
+        <v>43.30753196716309</v>
       </c>
       <c r="L16">
-        <v>10.70060895442963</v>
+        <v>38.26994416236877</v>
       </c>
       <c r="M16">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N16">
-        <v>1.03</v>
+        <v>1.08</v>
+      </c>
+      <c r="O16" t="s">
+        <v>78</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R16">
         <v>0</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>7.222222222222221</v>
       </c>
       <c r="U16" t="b">
         <v>0</v>
@@ -2413,46 +2539,46 @@
         <v>0</v>
       </c>
       <c r="X16">
-        <v>8.109999999999999</v>
+        <v>27.64</v>
       </c>
       <c r="Y16">
-        <v>12.43</v>
+        <v>47.25</v>
       </c>
       <c r="Z16">
-        <v>4.39</v>
+        <v>10.78</v>
       </c>
       <c r="AA16">
-        <v>-2.55</v>
+        <v>4.2</v>
       </c>
       <c r="AB16">
-        <v>85.28</v>
+        <v>25.75</v>
       </c>
       <c r="AC16">
-        <v>146.21</v>
+        <v>124.2</v>
       </c>
       <c r="AD16">
-        <v>0.58</v>
+        <v>45.47</v>
       </c>
       <c r="AE16">
-        <v>136.39</v>
+        <v>410.14</v>
       </c>
       <c r="AF16">
-        <v>-232.94</v>
+        <v>-48.89</v>
       </c>
       <c r="AG16">
-        <v>195.52</v>
+        <v>-14.01</v>
       </c>
       <c r="AH16" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="AI16" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AJ16" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="AK16">
-        <v>36.62747785161813</v>
+        <v>52.51288094505608</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2460,43 +2586,43 @@
         <v>52</v>
       </c>
       <c r="B17">
-        <v>94.23393739703459</v>
+        <v>96.03121516164994</v>
       </c>
       <c r="C17">
-        <v>211</v>
+        <v>709</v>
       </c>
       <c r="D17">
-        <v>12.68</v>
+        <v>100.91</v>
       </c>
       <c r="E17">
-        <v>2.41</v>
+        <v>2.22</v>
       </c>
       <c r="F17">
-        <v>-0.4868229137405758</v>
+        <v>0.4431293869759703</v>
       </c>
       <c r="G17">
-        <v>1.99</v>
+        <v>2.72</v>
       </c>
       <c r="H17">
-        <v>-0.8518983917272265</v>
+        <v>1.272371051827039</v>
       </c>
       <c r="I17">
-        <v>12.35492496490479</v>
+        <v>102.4580001831055</v>
       </c>
       <c r="J17">
-        <v>12.21238737106323</v>
+        <v>98.71350059509277</v>
       </c>
       <c r="K17">
-        <v>12.46932914733887</v>
+        <v>98.1300001525879</v>
       </c>
       <c r="L17">
-        <v>11.10607325553894</v>
+        <v>87.77125022888184</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N17">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -2517,52 +2643,52 @@
         <v>0</v>
       </c>
       <c r="V17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="b">
         <v>1</v>
       </c>
       <c r="X17">
-        <v>7.92</v>
+        <v>53.21</v>
       </c>
       <c r="Y17">
-        <v>13.45</v>
+        <v>104.54</v>
       </c>
       <c r="Z17">
-        <v>7.63</v>
+        <v>17.1</v>
       </c>
       <c r="AA17">
-        <v>-47.59</v>
+        <v>6.1</v>
       </c>
       <c r="AB17">
-        <v>87.5</v>
+        <v>165.08</v>
       </c>
       <c r="AC17">
-        <v>107.39</v>
+        <v>241.67</v>
       </c>
       <c r="AD17">
-        <v>3.36</v>
+        <v>5.41</v>
       </c>
       <c r="AE17">
-        <v>-65.91</v>
+        <v>4.94</v>
       </c>
       <c r="AF17">
-        <v>-57.69</v>
+        <v>32.79</v>
       </c>
       <c r="AG17">
-        <v>151.23</v>
+        <v>201.67</v>
       </c>
       <c r="AH17" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="AI17" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="AJ17" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="AK17">
-        <v>30.9728537386073</v>
+        <v>50.928360708053</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2570,43 +2696,43 @@
         <v>53</v>
       </c>
       <c r="B18">
-        <v>91.38620851965167</v>
+        <v>95.3623188405797</v>
       </c>
       <c r="C18">
-        <v>197</v>
+        <v>655</v>
       </c>
       <c r="D18">
-        <v>30.19</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="E18">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="F18">
-        <v>-1.467069729882617</v>
+        <v>0.2297809367570077</v>
       </c>
       <c r="G18">
-        <v>1.32</v>
+        <v>1.86</v>
       </c>
       <c r="H18">
-        <v>-1.494527987124326</v>
+        <v>-0.07327391780167719</v>
       </c>
       <c r="I18">
-        <v>29.65969543457031</v>
+        <v>69.59977569580079</v>
       </c>
       <c r="J18">
-        <v>29.4343373298645</v>
+        <v>64.73066349029541</v>
       </c>
       <c r="K18">
-        <v>29.61060096740723</v>
+        <v>63.20785484313965</v>
       </c>
       <c r="L18">
-        <v>27.98512020111084</v>
+        <v>57.57834732055664</v>
       </c>
       <c r="M18">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N18">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -2624,55 +2750,55 @@
         <v>0</v>
       </c>
       <c r="U18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" t="b">
         <v>1</v>
       </c>
       <c r="W18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18">
-        <v>22.02</v>
+        <v>37.61</v>
       </c>
       <c r="Y18">
-        <v>31.21</v>
+        <v>71.52</v>
       </c>
       <c r="Z18">
-        <v>14.55</v>
+        <v>8.59</v>
       </c>
       <c r="AA18">
-        <v>-218.9</v>
+        <v>6.93</v>
       </c>
       <c r="AB18">
-        <v>78.2</v>
+        <v>34.98</v>
       </c>
       <c r="AC18">
-        <v>81.84999999999999</v>
+        <v>251.28</v>
       </c>
       <c r="AD18">
-        <v>5.87</v>
+        <v>10.09</v>
       </c>
       <c r="AE18">
-        <v>-464.29</v>
+        <v>34.31</v>
       </c>
       <c r="AF18">
-        <v>-89.02</v>
+        <v>32.47</v>
       </c>
       <c r="AG18">
-        <v>145.37</v>
+        <v>97.44</v>
       </c>
       <c r="AH18" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="AI18" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AJ18" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="AK18">
-        <v>25.76278412640367</v>
+        <v>47.55149072731928</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2680,43 +2806,43 @@
         <v>54</v>
       </c>
       <c r="B19">
-        <v>95.52835961402683</v>
+        <v>91.75027870680044</v>
       </c>
       <c r="C19">
-        <v>1198</v>
+        <v>729</v>
       </c>
       <c r="D19">
-        <v>59.86</v>
+        <v>41.76</v>
       </c>
       <c r="E19">
-        <v>4.13</v>
+        <v>1.21</v>
       </c>
       <c r="F19">
-        <v>1.59468884399314</v>
+        <v>-0.6909860589248288</v>
       </c>
       <c r="G19">
-        <v>3.57</v>
+        <v>1.12</v>
       </c>
       <c r="H19">
-        <v>0.6635564750301122</v>
+        <v>-1.231154473063596</v>
       </c>
       <c r="I19">
-        <v>56.25400009155273</v>
+        <v>41.25999908447265</v>
       </c>
       <c r="J19">
-        <v>53.05200004577637</v>
+        <v>41.54300003051758</v>
       </c>
       <c r="K19">
-        <v>54.8889998626709</v>
+        <v>41.02180000305176</v>
       </c>
       <c r="L19">
-        <v>49.8992000579834</v>
+        <v>35.94509991645813</v>
       </c>
       <c r="M19">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="N19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -2734,55 +2860,55 @@
         <v>0</v>
       </c>
       <c r="U19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="b">
         <v>1</v>
       </c>
       <c r="W19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>31.75</v>
+        <v>24.79</v>
       </c>
       <c r="Y19">
-        <v>65.09</v>
+        <v>42.86</v>
       </c>
       <c r="Z19">
-        <v>2.22</v>
+        <v>17.35</v>
       </c>
       <c r="AA19">
-        <v>0.02</v>
+        <v>11.47</v>
       </c>
       <c r="AB19">
-        <v>74.48999999999999</v>
+        <v>53.98</v>
       </c>
       <c r="AC19">
-        <v>80</v>
+        <v>216.67</v>
       </c>
       <c r="AD19">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="AE19">
-        <v>17.39</v>
+        <v>-16.67</v>
       </c>
       <c r="AF19">
-        <v>12.2</v>
+        <v>4.59</v>
       </c>
       <c r="AG19">
-        <v>36.67</v>
+        <v>263.33</v>
       </c>
       <c r="AH19" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AI19" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="AJ19" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="AK19">
-        <v>25.25342084094764</v>
+        <v>47.18081385130473</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2790,43 +2916,43 @@
         <v>55</v>
       </c>
       <c r="B20">
-        <v>91.78630265944928</v>
+        <v>96.23188405797102</v>
       </c>
       <c r="C20">
-        <v>1010</v>
+        <v>2419.5</v>
       </c>
       <c r="D20">
-        <v>10.39</v>
+        <v>104.63</v>
       </c>
       <c r="E20">
-        <v>2.36</v>
+        <v>1.32</v>
       </c>
       <c r="F20">
-        <v>-0.5473319764653934</v>
+        <v>-0.5674685351138505</v>
       </c>
       <c r="G20">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="H20">
-        <v>-1.101277040687295</v>
+        <v>-0.6522141954326367</v>
       </c>
       <c r="I20">
-        <v>10.24483165740967</v>
+        <v>105.2425445556641</v>
       </c>
       <c r="J20">
-        <v>10.03327240943909</v>
+        <v>103.9257965087891</v>
       </c>
       <c r="K20">
-        <v>10.332287940979</v>
+        <v>100.848701171875</v>
       </c>
       <c r="L20">
-        <v>9.694646501541138</v>
+        <v>82.82608390808106</v>
       </c>
       <c r="M20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N20">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -2844,55 +2970,55 @@
         <v>0</v>
       </c>
       <c r="U20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20">
-        <v>7.64</v>
+        <v>49.67</v>
       </c>
       <c r="Y20">
-        <v>10.94</v>
+        <v>107.16</v>
       </c>
       <c r="Z20">
-        <v>1.13</v>
+        <v>2.28</v>
       </c>
       <c r="AA20" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="AB20">
-        <v>10.87</v>
+        <v>23.94</v>
       </c>
       <c r="AC20">
-        <v>64.29000000000001</v>
+        <v>200</v>
       </c>
       <c r="AD20">
-        <v>5.37</v>
+        <v>3.33</v>
       </c>
       <c r="AE20">
-        <v>72.5</v>
+        <v>-7.69</v>
       </c>
       <c r="AF20">
-        <v>-24.53</v>
+        <v>-26.14</v>
       </c>
       <c r="AG20">
-        <v>26.19</v>
+        <v>340</v>
       </c>
       <c r="AH20" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="AI20" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="AJ20" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="AK20">
-        <v>17.81507051009818</v>
+        <v>44.48263974132065</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -2900,43 +3026,43 @@
         <v>56</v>
       </c>
       <c r="B21">
-        <v>96.54036243822077</v>
+        <v>90.36789297658862</v>
       </c>
       <c r="C21">
-        <v>729</v>
+        <v>1883</v>
       </c>
       <c r="D21">
-        <v>97.97</v>
+        <v>197.23</v>
       </c>
       <c r="E21">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="F21">
-        <v>0.8322746536604416</v>
+        <v>0.3645273263689839</v>
       </c>
       <c r="G21">
-        <v>3.44</v>
+        <v>1.74</v>
       </c>
       <c r="H21">
-        <v>0.5388671505500781</v>
+        <v>-0.261038332168475</v>
       </c>
       <c r="I21">
-        <v>94.86799926757813</v>
+        <v>193.1636322021484</v>
       </c>
       <c r="J21">
-        <v>89.04699935913087</v>
+        <v>194.8201904296875</v>
       </c>
       <c r="K21">
-        <v>90.61580017089844</v>
+        <v>189.631591796875</v>
       </c>
       <c r="L21">
-        <v>85.99619998931885</v>
+        <v>171.6452607727051</v>
       </c>
       <c r="M21">
-        <v>1.07</v>
+        <v>0.99</v>
       </c>
       <c r="N21">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -2957,52 +3083,52 @@
         <v>0</v>
       </c>
       <c r="V21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21">
-        <v>52.17</v>
+        <v>129.18</v>
       </c>
       <c r="Y21">
-        <v>109.05</v>
+        <v>217</v>
       </c>
       <c r="Z21">
-        <v>14.25</v>
+        <v>7.84</v>
       </c>
       <c r="AA21">
-        <v>690</v>
+        <v>22.78</v>
       </c>
       <c r="AB21">
-        <v>6.15</v>
+        <v>1.39</v>
       </c>
       <c r="AC21">
-        <v>57.14</v>
+        <v>352.27</v>
       </c>
       <c r="AD21">
-        <v>5.63</v>
+        <v>19.59</v>
       </c>
       <c r="AE21">
-        <v>25.71</v>
+        <v>-39.7</v>
       </c>
       <c r="AF21">
-        <v>12.9</v>
+        <v>297.59</v>
       </c>
       <c r="AG21">
-        <v>10.71</v>
+        <v>88.64</v>
       </c>
       <c r="AH21" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="AI21" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="AJ21" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="AK21">
-        <v>14.71703369633735</v>
+        <v>44.12332247242929</v>
       </c>
     </row>
     <row r="22" spans="1:37">
@@ -3010,49 +3136,49 @@
         <v>57</v>
       </c>
       <c r="B22">
-        <v>90.39774064485762</v>
+        <v>96.36566332218506</v>
       </c>
       <c r="C22">
-        <v>1978</v>
+        <v>828</v>
       </c>
       <c r="D22">
-        <v>61.06</v>
+        <v>22.61</v>
       </c>
       <c r="E22">
-        <v>3.29</v>
+        <v>1.74</v>
       </c>
       <c r="F22">
-        <v>0.5781365902162089</v>
+        <v>-0.0958561714719343</v>
       </c>
       <c r="G22">
-        <v>2.92</v>
+        <v>1.61</v>
       </c>
       <c r="H22">
-        <v>0.04010985262994122</v>
+        <v>-0.4644497810658389</v>
       </c>
       <c r="I22">
-        <v>58.07200088500976</v>
+        <v>22.72000045776367</v>
       </c>
       <c r="J22">
-        <v>55.98350009918213</v>
+        <v>21.95200004577637</v>
       </c>
       <c r="K22">
-        <v>54.58720008850098</v>
+        <v>20.6946000289917</v>
       </c>
       <c r="L22">
-        <v>54.10090002059937</v>
+        <v>16.51125003814697</v>
       </c>
       <c r="M22">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N22">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -3061,58 +3187,58 @@
         <v>0</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>4.444444444444444</v>
       </c>
       <c r="U22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22">
-        <v>42.11</v>
+        <v>10.15</v>
       </c>
       <c r="Y22">
-        <v>66.41</v>
+        <v>23.5</v>
       </c>
       <c r="Z22">
-        <v>2.17</v>
+        <v>2.41</v>
       </c>
       <c r="AA22">
-        <v>110.73</v>
+        <v>704.86</v>
       </c>
       <c r="AB22">
-        <v>26.32</v>
+        <v>43.97</v>
       </c>
       <c r="AC22">
-        <v>34.37</v>
+        <v>47.83</v>
       </c>
       <c r="AD22">
-        <v>4.82</v>
+        <v>10.03</v>
       </c>
       <c r="AE22">
-        <v>7.5</v>
+        <v>17.24</v>
       </c>
       <c r="AF22">
-        <v>37.93</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="AG22">
-        <v>-9.380000000000001</v>
+        <v>-32.61</v>
       </c>
       <c r="AH22" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AI22" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="AJ22" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="AK22">
-        <v>7.940506294058109</v>
+        <v>40.0289216929999</v>
       </c>
     </row>
     <row r="23" spans="1:37">
@@ -3120,109 +3246,2205 @@
         <v>58</v>
       </c>
       <c r="B23">
-        <v>90.68016003765592</v>
+        <v>94.7603121516165</v>
       </c>
       <c r="C23">
-        <v>997</v>
+        <v>2170</v>
       </c>
       <c r="D23">
-        <v>343.44</v>
+        <v>99.16</v>
       </c>
       <c r="E23">
-        <v>1.85</v>
+        <v>1.02</v>
       </c>
       <c r="F23">
-        <v>-1.16452441625853</v>
+        <v>-0.9043345091437909</v>
       </c>
       <c r="G23">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="H23">
-        <v>-0.880672851222619</v>
+        <v>0.02060828938172136</v>
       </c>
       <c r="I23">
-        <v>340.9120056152344</v>
+        <v>99.72400207519532</v>
       </c>
       <c r="J23">
-        <v>341.9150039672851</v>
+        <v>96.3830005645752</v>
       </c>
       <c r="K23">
-        <v>342.6464007568359</v>
+        <v>89.35660018920899</v>
       </c>
       <c r="L23">
-        <v>307.1354512023926</v>
+        <v>83.19704975128174</v>
       </c>
       <c r="M23">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="N23">
+        <v>1.12</v>
+      </c>
+      <c r="P23">
+        <v>5</v>
+      </c>
+      <c r="Q23">
+        <v>3</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>7.222222222222221</v>
+      </c>
+      <c r="U23" t="b">
+        <v>1</v>
+      </c>
+      <c r="V23" t="b">
+        <v>1</v>
+      </c>
+      <c r="W23" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>53.35</v>
+      </c>
+      <c r="Y23">
+        <v>102</v>
+      </c>
+      <c r="Z23">
+        <v>1.43</v>
+      </c>
+      <c r="AA23">
+        <v>25.87</v>
+      </c>
+      <c r="AB23">
+        <v>2.66</v>
+      </c>
+      <c r="AC23">
+        <v>51.43</v>
+      </c>
+      <c r="AD23">
+        <v>4.13</v>
+      </c>
+      <c r="AE23">
+        <v>21.37</v>
+      </c>
+      <c r="AF23">
+        <v>22.43</v>
+      </c>
+      <c r="AG23">
+        <v>1.9</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>106</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>120</v>
+      </c>
+      <c r="AK23">
+        <v>39.32349907505422</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37">
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24">
+        <v>95.80824972129321</v>
+      </c>
+      <c r="C24">
+        <v>694</v>
+      </c>
+      <c r="D24">
+        <v>54.19</v>
+      </c>
+      <c r="E24">
+        <v>2.27</v>
+      </c>
+      <c r="F24">
+        <v>0.4992737159809602</v>
+      </c>
+      <c r="G24">
+        <v>2.12</v>
+      </c>
+      <c r="H24">
+        <v>0.333548979993051</v>
+      </c>
+      <c r="I24">
+        <v>52.4916488647461</v>
+      </c>
+      <c r="J24">
+        <v>48.71768703460693</v>
+      </c>
+      <c r="K24">
+        <v>50.47325416564941</v>
+      </c>
+      <c r="L24">
+        <v>42.98401010513306</v>
+      </c>
+      <c r="M24">
+        <v>1.08</v>
+      </c>
+      <c r="N24">
+        <v>1.04</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24" t="b">
+        <v>0</v>
+      </c>
+      <c r="V24" t="b">
+        <v>1</v>
+      </c>
+      <c r="W24" t="b">
+        <v>1</v>
+      </c>
+      <c r="X24">
+        <v>29.13</v>
+      </c>
+      <c r="Y24">
+        <v>57.08</v>
+      </c>
+      <c r="Z24">
+        <v>11.35</v>
+      </c>
+      <c r="AA24">
+        <v>1.37</v>
+      </c>
+      <c r="AB24">
+        <v>12.2</v>
+      </c>
+      <c r="AC24">
+        <v>119.05</v>
+      </c>
+      <c r="AD24">
+        <v>1.6</v>
+      </c>
+      <c r="AE24">
+        <v>166.67</v>
+      </c>
+      <c r="AF24">
+        <v>-25</v>
+      </c>
+      <c r="AG24">
+        <v>109.52</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>111</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>129</v>
+      </c>
+      <c r="AK24">
+        <v>37.99990333197604</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37">
+      <c r="A25" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25">
+        <v>92.19620958751393</v>
+      </c>
+      <c r="C25">
+        <v>1742</v>
+      </c>
+      <c r="D25">
+        <v>29.25</v>
+      </c>
+      <c r="E25">
+        <v>2.17</v>
+      </c>
+      <c r="F25">
+        <v>0.38698505797098</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>0.1457845656262532</v>
+      </c>
+      <c r="I25">
+        <v>29.31800003051758</v>
+      </c>
+      <c r="J25">
+        <v>28.24774980545044</v>
+      </c>
+      <c r="K25">
+        <v>27.82009994506836</v>
+      </c>
+      <c r="L25">
+        <v>26.66917494773865</v>
+      </c>
+      <c r="M25">
+        <v>1.04</v>
+      </c>
+      <c r="N25">
+        <v>1.05</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25" t="b">
+        <v>0</v>
+      </c>
+      <c r="V25" t="b">
+        <v>1</v>
+      </c>
+      <c r="W25" t="b">
+        <v>1</v>
+      </c>
+      <c r="X25">
+        <v>15.62</v>
+      </c>
+      <c r="Y25">
+        <v>31.34</v>
+      </c>
+      <c r="Z25">
+        <v>1.98</v>
+      </c>
+      <c r="AA25">
+        <v>-30.09</v>
+      </c>
+      <c r="AB25">
+        <v>53.08</v>
+      </c>
+      <c r="AC25">
+        <v>52.63</v>
+      </c>
+      <c r="AD25">
+        <v>4.81</v>
+      </c>
+      <c r="AE25">
+        <v>18.37</v>
+      </c>
+      <c r="AF25">
+        <v>-9.26</v>
+      </c>
+      <c r="AG25">
+        <v>42.11</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>107</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>130</v>
+      </c>
+      <c r="AK25">
+        <v>33.75763363261888</v>
+      </c>
+    </row>
+    <row r="26" spans="1:37">
+      <c r="A26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26">
+        <v>93.37792642140468</v>
+      </c>
+      <c r="C26">
+        <v>1052</v>
+      </c>
+      <c r="D26">
+        <v>22.06</v>
+      </c>
+      <c r="E26">
+        <v>1.74</v>
+      </c>
+      <c r="F26">
+        <v>-0.0958561714719343</v>
+      </c>
+      <c r="G26">
+        <v>1.92</v>
+      </c>
+      <c r="H26">
+        <v>0.02060828938172136</v>
+      </c>
+      <c r="I26">
+        <v>21.55040397644043</v>
+      </c>
+      <c r="J26">
+        <v>20.23349504470825</v>
+      </c>
+      <c r="K26">
+        <v>20.3309049987793</v>
+      </c>
+      <c r="L26">
+        <v>18.02908390522003</v>
+      </c>
+      <c r="M26">
+        <v>1.07</v>
+      </c>
+      <c r="N26">
+        <v>1.06</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26" t="b">
+        <v>0</v>
+      </c>
+      <c r="V26" t="b">
+        <v>1</v>
+      </c>
+      <c r="W26" t="b">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>11.48</v>
+      </c>
+      <c r="Y26">
+        <v>22.46</v>
+      </c>
+      <c r="Z26">
+        <v>2.76</v>
+      </c>
+      <c r="AA26">
+        <v>6.04</v>
+      </c>
+      <c r="AB26">
+        <v>57.58</v>
+      </c>
+      <c r="AC26">
+        <v>46.77</v>
+      </c>
+      <c r="AD26">
+        <v>6.06</v>
+      </c>
+      <c r="AE26">
+        <v>27.27</v>
+      </c>
+      <c r="AF26">
+        <v>27.68</v>
+      </c>
+      <c r="AG26">
+        <v>-9.68</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>96</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>107</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>131</v>
+      </c>
+      <c r="AK26">
+        <v>32.84808807307525</v>
+      </c>
+    </row>
+    <row r="27" spans="1:37">
+      <c r="A27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27">
+        <v>90.43478260869566</v>
+      </c>
+      <c r="C27">
+        <v>1615</v>
+      </c>
+      <c r="D27">
+        <v>127.92</v>
+      </c>
+      <c r="E27">
+        <v>1.15</v>
+      </c>
+      <c r="F27">
+        <v>-0.7583592537308169</v>
+      </c>
+      <c r="G27">
+        <v>1.5</v>
+      </c>
+      <c r="H27">
+        <v>-0.6365671609020702</v>
+      </c>
+      <c r="I27">
+        <v>127.5199279785156</v>
+      </c>
+      <c r="J27">
+        <v>122.2145645141602</v>
+      </c>
+      <c r="K27">
+        <v>119.8420910644531</v>
+      </c>
+      <c r="L27">
+        <v>111.3568789672852</v>
+      </c>
+      <c r="M27">
+        <v>1.04</v>
+      </c>
+      <c r="N27">
+        <v>1.06</v>
+      </c>
+      <c r="O27" t="s">
+        <v>79</v>
+      </c>
+      <c r="P27">
+        <v>3</v>
+      </c>
+      <c r="Q27">
+        <v>2</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>3.888888888888888</v>
+      </c>
+      <c r="U27" t="b">
+        <v>0</v>
+      </c>
+      <c r="V27" t="b">
+        <v>1</v>
+      </c>
+      <c r="W27" t="b">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>81.23</v>
+      </c>
+      <c r="Y27">
+        <v>130.32</v>
+      </c>
+      <c r="Z27">
+        <v>6.48</v>
+      </c>
+      <c r="AA27">
+        <v>2.98</v>
+      </c>
+      <c r="AB27">
+        <v>2.01</v>
+      </c>
+      <c r="AC27">
+        <v>49.07</v>
+      </c>
+      <c r="AD27">
+        <v>6.92</v>
+      </c>
+      <c r="AE27">
+        <v>36.36</v>
+      </c>
+      <c r="AF27">
+        <v>33.33</v>
+      </c>
+      <c r="AG27">
+        <v>-18.01</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>92</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>132</v>
+      </c>
+      <c r="AK27">
+        <v>32.69011698491348</v>
+      </c>
+    </row>
+    <row r="28" spans="1:37">
+      <c r="A28" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28">
+        <v>95.6298773690078</v>
+      </c>
+      <c r="C28">
+        <v>1407</v>
+      </c>
+      <c r="D28">
+        <v>10.84</v>
+      </c>
+      <c r="E28">
+        <v>2.16</v>
+      </c>
+      <c r="F28">
+        <v>0.3757561921699822</v>
+      </c>
+      <c r="G28">
+        <v>2.35</v>
+      </c>
+      <c r="H28">
+        <v>0.6934307741960798</v>
+      </c>
+      <c r="I28">
+        <v>10.78599987030029</v>
+      </c>
+      <c r="J28">
+        <v>10.68999991416931</v>
+      </c>
+      <c r="K28">
+        <v>10.11479999542236</v>
+      </c>
+      <c r="L28">
+        <v>9.266999995708465</v>
+      </c>
+      <c r="M28">
+        <v>1.01</v>
+      </c>
+      <c r="N28">
+        <v>1.07</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28" t="b">
+        <v>1</v>
+      </c>
+      <c r="V28" t="b">
+        <v>1</v>
+      </c>
+      <c r="W28" t="b">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>5.15</v>
+      </c>
+      <c r="Y28">
+        <v>11.4</v>
+      </c>
+      <c r="Z28">
+        <v>1.01</v>
+      </c>
+      <c r="AA28">
+        <v>61.02</v>
+      </c>
+      <c r="AB28">
+        <v>1001.18</v>
+      </c>
+      <c r="AC28">
+        <v>19.25</v>
+      </c>
+      <c r="AD28">
+        <v>17.21</v>
+      </c>
+      <c r="AE28">
+        <v>474.04</v>
+      </c>
+      <c r="AF28">
+        <v>-76.36</v>
+      </c>
+      <c r="AG28">
+        <v>-12.11</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ28" t="s">
+        <v>133</v>
+      </c>
+      <c r="AK28">
+        <v>31.60714157201819</v>
+      </c>
+    </row>
+    <row r="29" spans="1:37">
+      <c r="A29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29">
+        <v>92.68673355629878</v>
+      </c>
+      <c r="C29">
+        <v>2024</v>
+      </c>
+      <c r="D29">
+        <v>78.11</v>
+      </c>
+      <c r="E29">
+        <v>1.09</v>
+      </c>
+      <c r="F29">
+        <v>-0.8257324485368047</v>
+      </c>
+      <c r="G29">
+        <v>1.74</v>
+      </c>
+      <c r="H29">
+        <v>-0.261038332168475</v>
+      </c>
+      <c r="I29">
+        <v>78.29000091552734</v>
+      </c>
+      <c r="J29">
+        <v>74.93199920654297</v>
+      </c>
+      <c r="K29">
+        <v>71.79799957275391</v>
+      </c>
+      <c r="L29">
+        <v>70.064349899292</v>
+      </c>
+      <c r="M29">
+        <v>1.04</v>
+      </c>
+      <c r="N29">
+        <v>1.09</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29" t="b">
+        <v>0</v>
+      </c>
+      <c r="V29" t="b">
+        <v>1</v>
+      </c>
+      <c r="W29" t="b">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>36.92</v>
+      </c>
+      <c r="Y29">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="Z29">
+        <v>1.01</v>
+      </c>
+      <c r="AA29">
+        <v>0.87</v>
+      </c>
+      <c r="AB29">
+        <v>234.09</v>
+      </c>
+      <c r="AC29">
+        <v>27.91</v>
+      </c>
+      <c r="AD29">
+        <v>3.17</v>
+      </c>
+      <c r="AE29">
+        <v>1275</v>
+      </c>
+      <c r="AF29">
+        <v>-91.11</v>
+      </c>
+      <c r="AG29">
+        <v>4.65</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>104</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK29">
+        <v>31.45539817540636</v>
+      </c>
+    </row>
+    <row r="30" spans="1:37">
+      <c r="A30" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30">
+        <v>93.46711259754737</v>
+      </c>
+      <c r="C30">
+        <v>861</v>
+      </c>
+      <c r="D30">
+        <v>50.89</v>
+      </c>
+      <c r="E30">
+        <v>1.2</v>
+      </c>
+      <c r="F30">
+        <v>-0.7022149247258268</v>
+      </c>
+      <c r="G30">
+        <v>1.3</v>
+      </c>
+      <c r="H30">
+        <v>-0.9495078515133996</v>
+      </c>
+      <c r="I30">
+        <v>50.27932281494141</v>
+      </c>
+      <c r="J30">
+        <v>50.21011657714844</v>
+      </c>
+      <c r="K30">
+        <v>48.94579261779785</v>
+      </c>
+      <c r="L30">
+        <v>47.76625526428223</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>1.03</v>
+      </c>
+      <c r="P30">
+        <v>3</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="U30" t="b">
+        <v>1</v>
+      </c>
+      <c r="V30" t="b">
+        <v>1</v>
+      </c>
+      <c r="W30" t="b">
+        <v>1</v>
+      </c>
+      <c r="X30">
+        <v>31.67</v>
+      </c>
+      <c r="Y30">
+        <v>54.99</v>
+      </c>
+      <c r="Z30">
+        <v>12.21</v>
+      </c>
+      <c r="AA30">
+        <v>1.18</v>
+      </c>
+      <c r="AB30">
+        <v>106.49</v>
+      </c>
+      <c r="AC30">
+        <v>23.08</v>
+      </c>
+      <c r="AD30">
+        <v>0.7</v>
+      </c>
+      <c r="AE30">
+        <v>-11.11</v>
+      </c>
+      <c r="AF30">
+        <v>1000</v>
+      </c>
+      <c r="AG30">
+        <v>-115.38</v>
+      </c>
+      <c r="AH30" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>104</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK30">
+        <v>30.64856559399203</v>
+      </c>
+    </row>
+    <row r="31" spans="1:37">
+      <c r="A31" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31">
+        <v>93.4448160535117</v>
+      </c>
+      <c r="C31">
+        <v>1421</v>
+      </c>
+      <c r="D31">
+        <v>46.65</v>
+      </c>
+      <c r="E31">
+        <v>2.09</v>
+      </c>
+      <c r="F31">
+        <v>0.2971541315629959</v>
+      </c>
+      <c r="G31">
+        <v>2.07</v>
+      </c>
+      <c r="H31">
+        <v>0.2553138073402182</v>
+      </c>
+      <c r="I31">
+        <v>46.04200057983398</v>
+      </c>
+      <c r="J31">
+        <v>42.66799964904785</v>
+      </c>
+      <c r="K31">
+        <v>40.45579986572265</v>
+      </c>
+      <c r="L31">
+        <v>37.57044998168945</v>
+      </c>
+      <c r="M31">
+        <v>1.08</v>
+      </c>
+      <c r="N31">
+        <v>1.14</v>
+      </c>
+      <c r="P31">
+        <v>1</v>
+      </c>
+      <c r="Q31">
+        <v>2</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>2.777777777777778</v>
+      </c>
+      <c r="U31" t="b">
+        <v>0</v>
+      </c>
+      <c r="V31" t="b">
+        <v>1</v>
+      </c>
+      <c r="W31" t="b">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>29.78</v>
+      </c>
+      <c r="Y31">
+        <v>47.48</v>
+      </c>
+      <c r="Z31">
+        <v>1.88</v>
+      </c>
+      <c r="AA31">
+        <v>25.39</v>
+      </c>
+      <c r="AB31">
+        <v>120.69</v>
+      </c>
+      <c r="AC31">
+        <v>16.13</v>
+      </c>
+      <c r="AD31">
+        <v>3.49</v>
+      </c>
+      <c r="AE31">
+        <v>14.29</v>
+      </c>
+      <c r="AF31">
+        <v>6.78</v>
+      </c>
+      <c r="AG31">
+        <v>-4.84</v>
+      </c>
+      <c r="AH31" t="s">
+        <v>99</v>
+      </c>
+      <c r="AI31" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>136</v>
+      </c>
+      <c r="AK31">
+        <v>29.60404112306306</v>
+      </c>
+    </row>
+    <row r="32" spans="1:37">
+      <c r="A32" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32">
+        <v>97.54738015607582</v>
+      </c>
+      <c r="C32">
+        <v>932</v>
+      </c>
+      <c r="D32">
+        <v>20.44</v>
+      </c>
+      <c r="E32">
+        <v>0.8</v>
+      </c>
+      <c r="F32">
+        <v>-1.151369556765747</v>
+      </c>
+      <c r="G32">
+        <v>1.09</v>
+      </c>
+      <c r="H32">
+        <v>-1.278095576655295</v>
+      </c>
+      <c r="I32">
+        <v>20.23503799438476</v>
+      </c>
+      <c r="J32">
+        <v>19.54593133926392</v>
+      </c>
+      <c r="K32">
+        <v>18.58189960479736</v>
+      </c>
+      <c r="L32">
+        <v>15.93577142238617</v>
+      </c>
+      <c r="M32">
+        <v>1.04</v>
+      </c>
+      <c r="N32">
+        <v>1.09</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32" t="b">
+        <v>1</v>
+      </c>
+      <c r="V32" t="b">
+        <v>1</v>
+      </c>
+      <c r="W32" t="b">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>9.92</v>
+      </c>
+      <c r="Y32">
+        <v>20.57</v>
+      </c>
+      <c r="Z32">
+        <v>1.21</v>
+      </c>
+      <c r="AA32">
+        <v>0.38</v>
+      </c>
+      <c r="AB32">
+        <v>300</v>
+      </c>
+      <c r="AC32">
+        <v>16.67</v>
+      </c>
+      <c r="AD32">
+        <v>1.03</v>
+      </c>
+      <c r="AE32">
+        <v>7.69</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>8.33</v>
+      </c>
+      <c r="AH32" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>109</v>
+      </c>
+      <c r="AJ32" t="s">
+        <v>137</v>
+      </c>
+      <c r="AK32">
+        <v>27.35779199350623</v>
+      </c>
+    </row>
+    <row r="33" spans="1:37">
+      <c r="A33" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33">
+        <v>95.22853957636566</v>
+      </c>
+      <c r="C33">
+        <v>224</v>
+      </c>
+      <c r="D33">
+        <v>20.66</v>
+      </c>
+      <c r="E33">
+        <v>0.9</v>
+      </c>
+      <c r="F33">
+        <v>-1.039080898755767</v>
+      </c>
+      <c r="G33">
+        <v>1.4</v>
+      </c>
+      <c r="H33">
+        <v>-0.7930375062077351</v>
+      </c>
+      <c r="I33">
+        <v>20.9620002746582</v>
+      </c>
+      <c r="J33">
+        <v>20.55762500762939</v>
+      </c>
+      <c r="K33">
+        <v>20.1142000579834</v>
+      </c>
+      <c r="L33">
+        <v>17.43228754043579</v>
+      </c>
+      <c r="M33">
+        <v>1.02</v>
+      </c>
+      <c r="N33">
+        <v>1.04</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33" t="b">
+        <v>1</v>
+      </c>
+      <c r="V33" t="b">
+        <v>0</v>
+      </c>
+      <c r="W33" t="b">
+        <v>1</v>
+      </c>
+      <c r="X33">
+        <v>11.15</v>
+      </c>
+      <c r="Y33">
+        <v>21.33</v>
+      </c>
+      <c r="Z33">
+        <v>18.64</v>
+      </c>
+      <c r="AA33">
+        <v>242.91</v>
+      </c>
+      <c r="AB33">
+        <v>12.23</v>
+      </c>
+      <c r="AC33">
+        <v>34.69</v>
+      </c>
+      <c r="AD33">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="AE33">
+        <v>-22.35</v>
+      </c>
+      <c r="AF33">
+        <v>49.12</v>
+      </c>
+      <c r="AG33">
+        <v>16.33</v>
+      </c>
+      <c r="AH33" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ33" t="s">
+        <v>138</v>
+      </c>
+      <c r="AK33">
+        <v>26.41713377559408</v>
+      </c>
+    </row>
+    <row r="34" spans="1:37">
+      <c r="A34" t="s">
+        <v>69</v>
+      </c>
+      <c r="B34">
+        <v>95.65217391304348</v>
+      </c>
+      <c r="C34">
+        <v>1210</v>
+      </c>
+      <c r="D34">
+        <v>29.37</v>
+      </c>
+      <c r="E34">
+        <v>2.56</v>
+      </c>
+      <c r="F34">
+        <v>0.8249108242099025</v>
+      </c>
+      <c r="G34">
+        <v>2.8</v>
+      </c>
+      <c r="H34">
+        <v>1.39754732807157</v>
+      </c>
+      <c r="I34">
+        <v>30.32471923828125</v>
+      </c>
+      <c r="J34">
+        <v>27.64121046066284</v>
+      </c>
+      <c r="K34">
+        <v>26.87065574645996</v>
+      </c>
+      <c r="L34">
+        <v>19.88088461875915</v>
+      </c>
+      <c r="M34">
+        <v>1.1</v>
+      </c>
+      <c r="N34">
+        <v>1.13</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34" t="b">
+        <v>0</v>
+      </c>
+      <c r="V34" t="b">
+        <v>1</v>
+      </c>
+      <c r="W34" t="b">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>11.48</v>
+      </c>
+      <c r="Y34">
+        <v>32.27</v>
+      </c>
+      <c r="Z34">
+        <v>1.27</v>
+      </c>
+      <c r="AA34">
+        <v>9.73</v>
+      </c>
+      <c r="AB34">
+        <v>6.51</v>
+      </c>
+      <c r="AC34">
+        <v>31.37</v>
+      </c>
+      <c r="AD34">
+        <v>3.23</v>
+      </c>
+      <c r="AE34">
+        <v>8.06</v>
+      </c>
+      <c r="AF34">
+        <v>-36.73</v>
+      </c>
+      <c r="AG34">
+        <v>92.16</v>
+      </c>
+      <c r="AH34" t="s">
+        <v>83</v>
+      </c>
+      <c r="AI34" t="s">
+        <v>106</v>
+      </c>
+      <c r="AJ34" t="s">
+        <v>139</v>
+      </c>
+      <c r="AK34">
+        <v>24.09684198336742</v>
+      </c>
+    </row>
+    <row r="35" spans="1:37">
+      <c r="A35" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35">
+        <v>91.66109253065775</v>
+      </c>
+      <c r="C35">
+        <v>1665</v>
+      </c>
+      <c r="D35">
+        <v>220.15</v>
+      </c>
+      <c r="E35">
+        <v>1.56</v>
+      </c>
+      <c r="F35">
+        <v>-0.2979757558898984</v>
+      </c>
+      <c r="G35">
+        <v>1.81</v>
+      </c>
+      <c r="H35">
+        <v>-0.1515090904545096</v>
+      </c>
+      <c r="I35">
+        <v>222.3040008544922</v>
+      </c>
+      <c r="J35">
+        <v>221.2740005493164</v>
+      </c>
+      <c r="K35">
+        <v>217.0438003540039</v>
+      </c>
+      <c r="L35">
+        <v>196.1660998535156</v>
+      </c>
+      <c r="M35">
+        <v>1</v>
+      </c>
+      <c r="N35">
+        <v>1.02</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35" t="b">
+        <v>1</v>
+      </c>
+      <c r="V35" t="b">
+        <v>1</v>
+      </c>
+      <c r="W35" t="b">
+        <v>1</v>
+      </c>
+      <c r="X35">
+        <v>136.8</v>
+      </c>
+      <c r="Y35">
+        <v>229.2</v>
+      </c>
+      <c r="Z35">
+        <v>17.51</v>
+      </c>
+      <c r="AA35">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="AB35">
+        <v>12.47</v>
+      </c>
+      <c r="AC35">
+        <v>23.58</v>
+      </c>
+      <c r="AD35">
+        <v>3.9</v>
+      </c>
+      <c r="AE35">
+        <v>27.18</v>
+      </c>
+      <c r="AF35">
+        <v>-43.72</v>
+      </c>
+      <c r="AG35">
+        <v>72.64</v>
+      </c>
+      <c r="AH35" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI35" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ35" t="s">
+        <v>118</v>
+      </c>
+      <c r="AK35">
+        <v>22.89845954926849</v>
+      </c>
+    </row>
+    <row r="36" spans="1:37">
+      <c r="A36" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36">
+        <v>90.90301003344482</v>
+      </c>
+      <c r="C36">
+        <v>1198</v>
+      </c>
+      <c r="D36">
+        <v>62.03</v>
+      </c>
+      <c r="E36">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F36">
+        <v>-1.140140690964749</v>
+      </c>
+      <c r="G36">
+        <v>1.03</v>
+      </c>
+      <c r="H36">
+        <v>-1.371977783838694</v>
+      </c>
+      <c r="I36">
+        <v>61.31201248168945</v>
+      </c>
+      <c r="J36">
+        <v>60.77879009246826</v>
+      </c>
+      <c r="K36">
+        <v>59.87304893493652</v>
+      </c>
+      <c r="L36">
+        <v>53.68259283065796</v>
+      </c>
+      <c r="M36">
+        <v>1.01</v>
+      </c>
+      <c r="N36">
+        <v>1.02</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36" t="b">
+        <v>1</v>
+      </c>
+      <c r="V36" t="b">
+        <v>1</v>
+      </c>
+      <c r="W36" t="b">
+        <v>1</v>
+      </c>
+      <c r="X36">
+        <v>40.35</v>
+      </c>
+      <c r="Y36">
+        <v>62.27</v>
+      </c>
+      <c r="Z36">
+        <v>11.4</v>
+      </c>
+      <c r="AA36">
+        <v>41.59</v>
+      </c>
+      <c r="AB36">
+        <v>5.56</v>
+      </c>
+      <c r="AC36">
+        <v>25</v>
+      </c>
+      <c r="AD36">
+        <v>5.17</v>
+      </c>
+      <c r="AE36">
+        <v>34.62</v>
+      </c>
+      <c r="AF36">
+        <v>-58.73</v>
+      </c>
+      <c r="AG36">
+        <v>125</v>
+      </c>
+      <c r="AH36" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI36" t="s">
+        <v>109</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK36">
+        <v>21.67200472076976</v>
+      </c>
+    </row>
+    <row r="37" spans="1:37">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37">
+        <v>98.28316610925306</v>
+      </c>
+      <c r="C37">
+        <v>1866</v>
+      </c>
+      <c r="D37">
+        <v>61.27</v>
+      </c>
+      <c r="E37">
+        <v>2.16</v>
+      </c>
+      <c r="F37">
+        <v>0.3757561921699822</v>
+      </c>
+      <c r="G37">
+        <v>2.02</v>
+      </c>
+      <c r="H37">
+        <v>0.1770786346873862</v>
+      </c>
+      <c r="I37">
+        <v>59.45127334594726</v>
+      </c>
+      <c r="J37">
+        <v>58.44373264312744</v>
+      </c>
+      <c r="K37">
+        <v>55.70461738586426</v>
+      </c>
+      <c r="L37">
+        <v>49.43486763000488</v>
+      </c>
+      <c r="M37">
+        <v>1.02</v>
+      </c>
+      <c r="N37">
+        <v>1.07</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37" t="b">
+        <v>0</v>
+      </c>
+      <c r="V37" t="b">
+        <v>1</v>
+      </c>
+      <c r="W37" t="b">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>28.08</v>
+      </c>
+      <c r="Y37">
+        <v>62.67</v>
+      </c>
+      <c r="Z37">
+        <v>1.66</v>
+      </c>
+      <c r="AA37">
+        <v>-235.57</v>
+      </c>
+      <c r="AB37">
+        <v>2.06</v>
+      </c>
+      <c r="AC37">
+        <v>28</v>
+      </c>
+      <c r="AD37">
+        <v>9.18</v>
+      </c>
+      <c r="AE37">
+        <v>113.33</v>
+      </c>
+      <c r="AF37">
+        <v>-44.44</v>
+      </c>
+      <c r="AG37">
+        <v>8</v>
+      </c>
+      <c r="AH37" t="s">
+        <v>86</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>106</v>
+      </c>
+      <c r="AJ37" t="s">
+        <v>140</v>
+      </c>
+      <c r="AK37">
+        <v>20.84659444083509</v>
+      </c>
+    </row>
+    <row r="38" spans="1:37">
+      <c r="A38" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38">
+        <v>90.05574136008919</v>
+      </c>
+      <c r="C38">
+        <v>1058</v>
+      </c>
+      <c r="D38">
+        <v>237.87</v>
+      </c>
+      <c r="E38">
+        <v>2.51</v>
+      </c>
+      <c r="F38">
+        <v>0.7687664952049121</v>
+      </c>
+      <c r="G38">
+        <v>2.37</v>
+      </c>
+      <c r="H38">
+        <v>0.7247248432572128</v>
+      </c>
+      <c r="I38">
+        <v>231.2579986572266</v>
+      </c>
+      <c r="J38">
+        <v>208.4289993286133</v>
+      </c>
+      <c r="K38">
+        <v>205.01919921875</v>
+      </c>
+      <c r="L38">
+        <v>200.6708493804932</v>
+      </c>
+      <c r="M38">
+        <v>1.11</v>
+      </c>
+      <c r="N38">
+        <v>1.13</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38" t="b">
+        <v>0</v>
+      </c>
+      <c r="V38" t="b">
+        <v>1</v>
+      </c>
+      <c r="W38" t="b">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>140.95</v>
+      </c>
+      <c r="Y38">
+        <v>241.76</v>
+      </c>
+      <c r="Z38">
+        <v>11.28</v>
+      </c>
+      <c r="AA38">
+        <v>84.04000000000001</v>
+      </c>
+      <c r="AB38">
+        <v>14.5</v>
+      </c>
+      <c r="AC38">
+        <v>17.76</v>
+      </c>
+      <c r="AD38">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="AE38">
+        <v>10.53</v>
+      </c>
+      <c r="AF38">
+        <v>6.54</v>
+      </c>
+      <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI38" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ38" t="s">
+        <v>141</v>
+      </c>
+      <c r="AK38">
+        <v>20.66111300209443</v>
+      </c>
+    </row>
+    <row r="39" spans="1:37">
+      <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39">
+        <v>91.6164994425864</v>
+      </c>
+      <c r="C39">
+        <v>3107</v>
+      </c>
+      <c r="D39">
+        <v>67.45999999999999</v>
+      </c>
+      <c r="E39">
+        <v>0.84</v>
+      </c>
+      <c r="F39">
+        <v>-1.106454093561755</v>
+      </c>
+      <c r="G39">
+        <v>1.39</v>
+      </c>
+      <c r="H39">
+        <v>-0.8086845407383015</v>
+      </c>
+      <c r="I39">
+        <v>66.9837631225586</v>
+      </c>
+      <c r="J39">
+        <v>64.87670459747315</v>
+      </c>
+      <c r="K39">
+        <v>65.90290611267091</v>
+      </c>
+      <c r="L39">
+        <v>61.40001596450806</v>
+      </c>
+      <c r="M39">
+        <v>1.03</v>
+      </c>
+      <c r="N39">
+        <v>1.02</v>
+      </c>
+      <c r="O39" t="s">
+        <v>78</v>
+      </c>
+      <c r="P39">
+        <v>2</v>
+      </c>
+      <c r="Q39">
+        <v>1</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>2.222222222222222</v>
+      </c>
+      <c r="U39" t="b">
+        <v>1</v>
+      </c>
+      <c r="V39" t="b">
+        <v>1</v>
+      </c>
+      <c r="W39" t="b">
+        <v>1</v>
+      </c>
+      <c r="X39">
+        <v>43.35</v>
+      </c>
+      <c r="Y39">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="Z39">
+        <v>1.01</v>
+      </c>
+      <c r="AA39">
+        <v>229.98</v>
+      </c>
+      <c r="AB39">
+        <v>651.16</v>
+      </c>
+      <c r="AC39">
+        <v>3.06</v>
+      </c>
+      <c r="AD39">
+        <v>5.54</v>
+      </c>
+      <c r="AE39">
+        <v>10.99</v>
+      </c>
+      <c r="AF39">
+        <v>175.76</v>
+      </c>
+      <c r="AG39">
+        <v>-66.33</v>
+      </c>
+      <c r="AH39" t="s">
+        <v>102</v>
+      </c>
+      <c r="AI39" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ39" t="s">
+        <v>142</v>
+      </c>
+      <c r="AK39">
+        <v>19.01222934849311</v>
+      </c>
+    </row>
+    <row r="40" spans="1:37">
+      <c r="A40" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40">
+        <v>96.61092530657747</v>
+      </c>
+      <c r="C40">
+        <v>539</v>
+      </c>
+      <c r="D40">
+        <v>59.93</v>
+      </c>
+      <c r="E40">
+        <v>2.03</v>
+      </c>
+      <c r="F40">
+        <v>0.2297809367570077</v>
+      </c>
+      <c r="G40">
+        <v>1.82</v>
+      </c>
+      <c r="H40">
+        <v>-0.1358620559239431</v>
+      </c>
+      <c r="I40">
+        <v>61.72732849121094</v>
+      </c>
+      <c r="J40">
+        <v>59.63444442749024</v>
+      </c>
+      <c r="K40">
+        <v>56.90147262573242</v>
+      </c>
+      <c r="L40">
+        <v>46.75409050941467</v>
+      </c>
+      <c r="M40">
+        <v>1.04</v>
+      </c>
+      <c r="N40">
+        <v>1.08</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>1</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="U40" t="b">
+        <v>0</v>
+      </c>
+      <c r="V40" t="b">
+        <v>0</v>
+      </c>
+      <c r="W40" t="b">
+        <v>1</v>
+      </c>
+      <c r="X40">
+        <v>27.95</v>
+      </c>
+      <c r="Y40">
+        <v>64.06</v>
+      </c>
+      <c r="Z40">
+        <v>10.23</v>
+      </c>
+      <c r="AA40">
+        <v>205.62</v>
+      </c>
+      <c r="AB40">
+        <v>47.87</v>
+      </c>
+      <c r="AC40">
+        <v>2.56</v>
+      </c>
+      <c r="AD40">
+        <v>9.16</v>
+      </c>
+      <c r="AE40">
+        <v>40.35</v>
+      </c>
+      <c r="AF40">
+        <v>-9.52</v>
+      </c>
+      <c r="AG40">
+        <v>-19.23</v>
+      </c>
+      <c r="AH40" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI40" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ40" t="s">
+        <v>143</v>
+      </c>
+      <c r="AK40">
+        <v>9.502700492490071</v>
+      </c>
+    </row>
+    <row r="41" spans="1:37">
+      <c r="A41" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41">
+        <v>92.4860646599777</v>
+      </c>
+      <c r="C41">
+        <v>1411</v>
+      </c>
+      <c r="D41">
+        <v>518.8099999999999</v>
+      </c>
+      <c r="E41">
+        <v>0.77</v>
+      </c>
+      <c r="F41">
+        <v>-1.185056154168741</v>
+      </c>
+      <c r="G41">
+        <v>1.23</v>
+      </c>
+      <c r="H41">
+        <v>-1.059037093227365</v>
+      </c>
+      <c r="I41">
+        <v>519.62373046875</v>
+      </c>
+      <c r="J41">
+        <v>522.3611694335938</v>
+      </c>
+      <c r="K41">
+        <v>516.0040368652344</v>
+      </c>
+      <c r="L41">
+        <v>448.5896780395508</v>
+      </c>
+      <c r="M41">
         <v>0.99</v>
       </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23" t="b">
-        <v>1</v>
-      </c>
-      <c r="V23" t="b">
-        <v>1</v>
-      </c>
-      <c r="W23" t="b">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>217.64</v>
-      </c>
-      <c r="Y23">
-        <v>363.2</v>
-      </c>
-      <c r="Z23">
-        <v>28.28</v>
-      </c>
-      <c r="AA23">
-        <v>6.02</v>
-      </c>
-      <c r="AB23">
-        <v>3.95</v>
-      </c>
-      <c r="AC23">
-        <v>28.25</v>
-      </c>
-      <c r="AD23">
-        <v>73.47</v>
-      </c>
-      <c r="AE23">
-        <v>5.09</v>
-      </c>
-      <c r="AF23">
-        <v>18.36</v>
-      </c>
-      <c r="AG23">
-        <v>3.11</v>
-      </c>
-      <c r="AH23" t="s">
-        <v>75</v>
-      </c>
-      <c r="AI23" t="s">
+      <c r="N41">
+        <v>1.01</v>
+      </c>
+      <c r="P41">
+        <v>1</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0.5555555555555555</v>
+      </c>
+      <c r="U41" t="b">
+        <v>1</v>
+      </c>
+      <c r="V41" t="b">
+        <v>0</v>
+      </c>
+      <c r="W41" t="b">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>302.25</v>
+      </c>
+      <c r="Y41">
+        <v>558.35</v>
+      </c>
+      <c r="Z41">
+        <v>45.18</v>
+      </c>
+      <c r="AA41">
+        <v>-7.24</v>
+      </c>
+      <c r="AB41">
+        <v>9.59</v>
+      </c>
+      <c r="AC41">
+        <v>2.9</v>
+      </c>
+      <c r="AD41">
+        <v>1.38</v>
+      </c>
+      <c r="AE41">
+        <v>-16.47</v>
+      </c>
+      <c r="AF41">
+        <v>18.06</v>
+      </c>
+      <c r="AG41">
+        <v>4.35</v>
+      </c>
+      <c r="AH41" t="s">
+        <v>90</v>
+      </c>
+      <c r="AI41" t="s">
+        <v>109</v>
+      </c>
+      <c r="AJ41" t="s">
+        <v>144</v>
+      </c>
+      <c r="AK41">
+        <v>5.674452783445614</v>
+      </c>
+    </row>
+    <row r="42" spans="1:37">
+      <c r="A42" t="s">
         <v>77</v>
       </c>
-      <c r="AJ23" t="s">
-        <v>105</v>
-      </c>
-      <c r="AK23">
-        <v>1.241695210112356</v>
+      <c r="B42">
+        <v>95.29542920847268</v>
+      </c>
+      <c r="C42">
+        <v>1821</v>
+      </c>
+      <c r="D42">
+        <v>51.54</v>
+      </c>
+      <c r="E42">
+        <v>2.7</v>
+      </c>
+      <c r="F42">
+        <v>0.9821149454238747</v>
+      </c>
+      <c r="G42">
+        <v>1.97</v>
+      </c>
+      <c r="H42">
+        <v>0.09884346203455377</v>
+      </c>
+      <c r="I42">
+        <v>47.01284713745117</v>
+      </c>
+      <c r="J42">
+        <v>45.99395732879638</v>
+      </c>
+      <c r="K42">
+        <v>46.53614234924316</v>
+      </c>
+      <c r="L42">
+        <v>41.47120281219483</v>
+      </c>
+      <c r="M42">
+        <v>1.02</v>
+      </c>
+      <c r="N42">
+        <v>1.01</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42" t="b">
+        <v>0</v>
+      </c>
+      <c r="V42" t="b">
+        <v>1</v>
+      </c>
+      <c r="W42" t="b">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>26.79</v>
+      </c>
+      <c r="Y42">
+        <v>51.65</v>
+      </c>
+      <c r="Z42">
+        <v>1.5</v>
+      </c>
+      <c r="AA42">
+        <v>35.59</v>
+      </c>
+      <c r="AB42">
+        <v>1.2</v>
+      </c>
+      <c r="AC42">
+        <v>3.08</v>
+      </c>
+      <c r="AD42">
+        <v>5.64</v>
+      </c>
+      <c r="AE42">
+        <v>11.67</v>
+      </c>
+      <c r="AF42">
+        <v>0</v>
+      </c>
+      <c r="AG42">
+        <v>-7.69</v>
+      </c>
+      <c r="AH42" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI42" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ42" t="s">
+        <v>121</v>
+      </c>
+      <c r="AK42">
+        <v>1.302442539259274</v>
       </c>
     </row>
   </sheetData>
